--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2943F1-C3D6-4C7D-9241-1387F743205B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E404C5A-17AB-4F01-B16E-6AC5D0794B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Bills Of Material" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>No.</t>
   </si>
@@ -66,13 +66,28 @@
   </si>
   <si>
     <t>Marble Station with ESP32</t>
+  </si>
+  <si>
+    <t>Servo Motor</t>
+  </si>
+  <si>
+    <t>Servo Motor 180</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1o-F_MPZrxvgcB_fcxiyyhbE7Jak8m61UF-xSTBCvfaY/edit?gid=2086349135#gid=2086349135</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +121,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -292,17 +315,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -312,6 +333,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -327,31 +354,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -369,14 +395,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -710,92 +729,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5785CA-F4AE-4464-AE2C-5F7A426F62CB}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="42.375" customWidth="1"/>
+    <col min="2" max="2" width="42.42578125" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="25.5" customWidth="1"/>
-    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="10"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12"/>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
     </row>
-    <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="16">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="15">
+        <v>3</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="16">
+        <v>2</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="17" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A1:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"In Stock"</formula>
+  <conditionalFormatting sqref="G4:G5">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Not ordered"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Not ordered"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G5" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" location="gid=2086349135" xr:uid="{D19C5093-5F1E-43F6-A2F5-6AD80406CC4D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E404C5A-17AB-4F01-B16E-6AC5D0794B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48181BF-D7D5-4210-9D29-7B3FEE1217A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="7305" yWindow="3045" windowWidth="24045" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bills Of Material" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>No.</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>ESP32-C3 Supermini</t>
-  </si>
-  <si>
     <t>Main controller (Wi-Fi + Bluetooth)</t>
   </si>
   <si>
@@ -77,7 +74,31 @@
     <t>Link</t>
   </si>
   <si>
-    <t>https://docs.google.com/spreadsheets/d/1o-F_MPZrxvgcB_fcxiyyhbE7Jak8m61UF-xSTBCvfaY/edit?gid=2086349135#gid=2086349135</t>
+    <t>USB-C Cable</t>
+  </si>
+  <si>
+    <t>USB-C Cable 3m</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/ANMIEL-Typ-C-Kabel-Ladekabel-Datenkabel-geflochten/dp/B09C3HH7KJ/ref=sr_1_6?__mk_de_DE=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=1HUJ8X6PSQNU8&amp;dib=eyJ2IjoiMSJ9.ZH0eL8XvX3DTxCgYcgGTokPY-OCGP9OmCfUbJRX_O8dVp8Y1XLwoEsrPFcvnPVLZvmFR-zCeVbO2opkI9v6wstHb3PzAZOQLPOyeihnSe59NsRuwoXQmF8VlHnoIDHRuSmQaxgReVVoqtUnIHtv6TfrKTgO9Kh6iiAGngLh5Ulc8iYjsqR6B1GuoUGYiygCZirhfQUZHJkvbFNL__RF-xSf5BIU2C9X4cmz_-YjN3Lo.3DULeIhGb1u3SODSffwhRyhMYPrRy90LZrRDQ7fSg-g&amp;dib_tag=se&amp;keywords=usb%2Bc%2Bkabel%2Bdata%2B3m&amp;qid=1761953154&amp;sprefix=usb%2Bc%2Bkabel%2Bdata%2B3m%2Caps%2C103&amp;sr=8-6&amp;th=1</t>
+  </si>
+  <si>
+    <t>Not ordered</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Cable for slaves (up to 25m)</t>
+  </si>
+  <si>
+    <t>ESP-WROOM-32 ESP32-S</t>
   </si>
 </sst>
 </file>
@@ -85,9 +106,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +150,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -319,7 +346,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -336,41 +363,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -729,35 +760,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5785CA-F4AE-4464-AE2C-5F7A426F62CB}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" style="11" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="8"/>
+      <c r="A1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -773,10 +804,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>4</v>
@@ -786,49 +817,96 @@
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="16">
-        <v>1</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="E4" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="10">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>6</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="15">
-        <v>3</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="16">
-        <v>2</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="17" t="s">
-        <v>7</v>
+      <c r="E5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="10">
+        <v>8.15</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G5">
+  <phoneticPr fontId="6" type="noConversion"/>
+  <conditionalFormatting sqref="G4:G7">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -840,14 +918,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G5" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G7" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" location="gid=2086349135" xr:uid="{D19C5093-5F1E-43F6-A2F5-6AD80406CC4D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48181BF-D7D5-4210-9D29-7B3FEE1217A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A43CF9-DDF2-493D-8D59-10072326EF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7305" yWindow="3045" windowWidth="24045" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bills Of Material" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
   <si>
     <t>No.</t>
   </si>
@@ -56,21 +56,12 @@
     <t>Main controller (Wi-Fi + Bluetooth)</t>
   </si>
   <si>
-    <t>In stock</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
     <t>Marble Station with ESP32</t>
   </si>
   <si>
-    <t>Servo Motor</t>
-  </si>
-  <si>
-    <t>Servo Motor 180</t>
-  </si>
-  <si>
     <t>Link</t>
   </si>
   <si>
@@ -89,16 +80,88 @@
     <t>-</t>
   </si>
   <si>
-    <t>Cable</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>Cable for slaves (up to 25m)</t>
-  </si>
-  <si>
-    <t>ESP-WROOM-32 ESP32-S</t>
+    <t>3D-Printer</t>
+  </si>
+  <si>
+    <t>3D Printer up to 250€</t>
+  </si>
+  <si>
+    <t>(black Friday)</t>
+  </si>
+  <si>
+    <t>Servo SG90 9g</t>
+  </si>
+  <si>
+    <t>Ali Express</t>
+  </si>
+  <si>
+    <t>Servo Motor 180 6x</t>
+  </si>
+  <si>
+    <t>Cable 22 AWG</t>
+  </si>
+  <si>
+    <t>Cable 18 AWG</t>
+  </si>
+  <si>
+    <t>Cable 18 AWG RED/Black</t>
+  </si>
+  <si>
+    <t>Ali Express USB-C Cable 3m</t>
+  </si>
+  <si>
+    <t>PLA-Filament</t>
+  </si>
+  <si>
+    <t>3D Printer 1kg Filament</t>
+  </si>
+  <si>
+    <t>Adapter 5V 3A</t>
+  </si>
+  <si>
+    <t>Netzteil Adapter AC 220V DC  5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prototype Board </t>
+  </si>
+  <si>
+    <t>5x7 ; 4x6 @ 2.54</t>
+  </si>
+  <si>
+    <t>ESP-32 38Pin CP2102</t>
+  </si>
+  <si>
+    <t>122 Stück Elektrolytkondensator 16 V 25 V 50 V Aluminium</t>
+  </si>
+  <si>
+    <t>Small Fuse</t>
+  </si>
+  <si>
+    <t>Small Fuse &amp; Holder 3A 5 Set</t>
+  </si>
+  <si>
+    <t>Power Jack Port</t>
+  </si>
+  <si>
+    <t>5,5X2,5 MM DC Power Jack Buchse Stecker DC005 10x</t>
+  </si>
+  <si>
+    <t>2200uF 16V 10 pcs</t>
+  </si>
+  <si>
+    <t>El. Capacitors</t>
+  </si>
+  <si>
+    <t>Cer. Capacitors</t>
+  </si>
+  <si>
+    <t>300 teile/los 50 V 2PF-0,1 UF 30</t>
+  </si>
+  <si>
+    <t>Gravi Tax Marble Run</t>
+  </si>
+  <si>
+    <t>Gravi Tax Base</t>
   </si>
 </sst>
 </file>
@@ -157,7 +220,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,6 +233,18 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -346,7 +421,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,6 +477,33 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -760,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5785CA-F4AE-4464-AE2C-5F7A426F62CB}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
@@ -772,7 +874,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -804,10 +906,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>4</v>
@@ -818,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -827,13 +929,13 @@
         <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="10">
-        <v>3</v>
+        <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -841,45 +943,46 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="10">
+        <f>C5 * 3.69</f>
+        <v>7.38</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="C6" s="21">
+        <v>1</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="E6" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="23">
         <v>8.15</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -887,18 +990,299 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1.89</v>
+      </c>
       <c r="G7" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="10">
+        <f>C8 * 8.29</f>
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="10">
+        <f>C9 * 2.47</f>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="24">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="25">
+        <v>1</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>15</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="27">
+        <v>250</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="24">
+        <v>8</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="25">
+        <v>1</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="10">
+        <f>C13 * 2.89</f>
+        <v>5.78</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1.69</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1.35</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="10">
+        <v>3.69</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1.94</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1.69</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +1290,7 @@
     <mergeCell ref="A1:G2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G7">
+  <conditionalFormatting sqref="G4:G19">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -918,7 +1302,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G7" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G19" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A43CF9-DDF2-493D-8D59-10072326EF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4EBF8C-E846-4019-8126-162ECD6E215D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
   <si>
     <t>No.</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Marble Station with ESP32</t>
   </si>
   <si>
-    <t>Link</t>
-  </si>
-  <si>
     <t>USB-C Cable</t>
   </si>
   <si>
@@ -134,12 +131,6 @@
     <t>122 Stück Elektrolytkondensator 16 V 25 V 50 V Aluminium</t>
   </si>
   <si>
-    <t>Small Fuse</t>
-  </si>
-  <si>
-    <t>Small Fuse &amp; Holder 3A 5 Set</t>
-  </si>
-  <si>
     <t>Power Jack Port</t>
   </si>
   <si>
@@ -162,6 +153,27 @@
   </si>
   <si>
     <t>Gravi Tax Base</t>
+  </si>
+  <si>
+    <t>PCB Production</t>
+  </si>
+  <si>
+    <t>Jack Power PCB</t>
+  </si>
+  <si>
+    <t>JLCPcb</t>
+  </si>
+  <si>
+    <t>Ordered</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>SMD Electrolytic Cap.</t>
+  </si>
+  <si>
+    <t>16V 1000uF 10x10.2</t>
   </si>
 </sst>
 </file>
@@ -235,13 +247,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,6 +472,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -478,18 +505,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -501,9 +516,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -862,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5785CA-F4AE-4464-AE2C-5F7A426F62CB}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
@@ -873,24 +885,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -906,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
@@ -920,7 +932,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -929,13 +941,13 @@
         <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="10">
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -943,46 +955,46 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="7">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="10">
         <f>C5 * 3.69</f>
         <v>7.38</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="25">
         <v>3</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="26">
+        <v>1</v>
+      </c>
+      <c r="D6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="21">
-        <v>1</v>
-      </c>
-      <c r="D6" s="21" t="s">
+      <c r="E6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="23">
+      <c r="F6" s="28">
         <v>8.15</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -990,22 +1002,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" s="10">
         <v>1.89</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1013,23 +1025,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="10">
         <f>C8 * 8.29</f>
         <v>8.2899999999999991</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1037,67 +1049,67 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="7">
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="10">
         <f>C9 * 2.47</f>
         <v>4.9400000000000004</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>7</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="15">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="17">
+        <v>250</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>8</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="15">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="24">
-        <v>7</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="25">
-        <v>1</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="27">
-        <v>250</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
-        <v>8</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="25">
-        <v>1</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1105,22 +1117,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="10">
         <v>3.7</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1128,23 +1140,23 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="7">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="10">
         <f>C13 * 2.89</f>
         <v>5.78</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1152,22 +1164,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>33</v>
+        <v>3</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F14" s="10">
-        <v>1.69</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1175,22 +1187,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" s="10">
         <v>1.35</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1198,22 +1210,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" s="7">
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
         <v>3.69</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1221,22 +1233,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="10">
         <v>1.94</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,22 +1256,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>39</v>
+      <c r="D18" s="18" t="s">
+        <v>36</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" s="10">
         <v>1.69</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1267,22 +1279,45 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C19" s="7">
         <v>2</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>41</v>
+      <c r="D19" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F19" s="10">
+        <v>1.99</v>
       </c>
       <c r="G19" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="7">
+        <v>3</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>12</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1290,7 +1325,7 @@
     <mergeCell ref="A1:G2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G19">
+  <conditionalFormatting sqref="G4:G20">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -1302,7 +1337,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G19" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G20" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4EBF8C-E846-4019-8126-162ECD6E215D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB1A96A-FAEC-4977-A487-752C99074440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bills Of Material" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="47">
   <si>
     <t>No.</t>
   </si>
@@ -113,12 +113,6 @@
     <t>3D Printer 1kg Filament</t>
   </si>
   <si>
-    <t>Adapter 5V 3A</t>
-  </si>
-  <si>
-    <t>Netzteil Adapter AC 220V DC  5V</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prototype Board </t>
   </si>
   <si>
@@ -174,6 +168,15 @@
   </si>
   <si>
     <t>16V 1000uF 10x10.2</t>
+  </si>
+  <si>
+    <t>Adapter 5V 10A</t>
+  </si>
+  <si>
+    <t>Netzteil Adapter AC 220V DC  5V 10A</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/gp/product/B0DM97JMVS/ref=sw_img_1?smid=A6FTR3WNTF6EM&amp;th=1</t>
   </si>
 </sst>
 </file>
@@ -487,6 +490,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -504,18 +519,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -885,24 +888,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -918,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
@@ -932,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -975,22 +978,22 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+      <c r="A6" s="19">
         <v>3</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="20">
         <v>1</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="22">
         <v>8.15</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -1117,19 +1120,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>17</v>
+        <v>45</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="F12" s="10">
-        <v>3.7</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>11</v>
@@ -1140,13 +1143,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="7">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
@@ -1164,22 +1167,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="7">
         <v>3</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F14" s="10">
         <v>9.5500000000000007</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1187,13 +1190,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>17</v>
@@ -1210,13 +1213,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="7">
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>17</v>
@@ -1233,13 +1236,13 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>17</v>
@@ -1256,13 +1259,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>17</v>
@@ -1279,13 +1282,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C19" s="7">
         <v>2</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>17</v>
@@ -1302,13 +1305,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" s="7">
         <v>3</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>12</v>
@@ -1336,12 +1339,15 @@
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G20" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E12" r:id="rId1" xr:uid="{E8A5AAF1-A457-44FF-B03E-B13CD56D10C7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB1A96A-FAEC-4977-A487-752C99074440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A15C8E9-D928-488E-B372-50AD469C1D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bills Of Material" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -116,15 +116,9 @@
     <t xml:space="preserve">Prototype Board </t>
   </si>
   <si>
-    <t>5x7 ; 4x6 @ 2.54</t>
-  </si>
-  <si>
     <t>ESP-32 38Pin CP2102</t>
   </si>
   <si>
-    <t>122 Stück Elektrolytkondensator 16 V 25 V 50 V Aluminium</t>
-  </si>
-  <si>
     <t>Power Jack Port</t>
   </si>
   <si>
@@ -152,9 +146,6 @@
     <t>PCB Production</t>
   </si>
   <si>
-    <t>Jack Power PCB</t>
-  </si>
-  <si>
     <t>JLCPcb</t>
   </si>
   <si>
@@ -177,6 +168,54 @@
   </si>
   <si>
     <t>https://www.amazon.de/gp/product/B0DM97JMVS/ref=sw_img_1?smid=A6FTR3WNTF6EM&amp;th=1</t>
+  </si>
+  <si>
+    <t>Motor Driver</t>
+  </si>
+  <si>
+    <t>DRV883</t>
+  </si>
+  <si>
+    <t>Micro DC Motor</t>
+  </si>
+  <si>
+    <t>Micro DC Motor 3 V-6 V 8000 U/min 10x</t>
+  </si>
+  <si>
+    <t>9x7 ; 4x6 @ 2.54</t>
+  </si>
+  <si>
+    <t>120 Stück Elektrolytkondensator 16 V 25 V 50 V Aluminium</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TCRT5000</t>
+  </si>
+  <si>
+    <t>Infrarot Reflektierende Sensor IR 10x</t>
+  </si>
+  <si>
+    <t>Solder Station</t>
+  </si>
+  <si>
+    <t>Lötstation Lötset 60W Lötkolben</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/Ravensburger-Starter-Set-Kugelbahnsystem-Konstruktionsspielzeug-Produktlinien/dp/B0BSXKTRYZ/ref=sxbs_pa_sp_search_thematic_btf_sspa?__mk_de_DE=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;content-id=amzn1.sym.14238797-2284-4030-be73-f85ec6483cda%3Aamzn1.sym.14238797-2284-4030-be73-f85ec6483cda&amp;crid=1Y7HZQ6BRLAEP&amp;cv_ct_cx=Kugelbahn&amp;keywords=Kugelbahn&amp;pd_rd_i=B0BSXKTRYZ&amp;pd_rd_r=5c0fa807-2c90-4dd4-bcd8-5df0ae05cffd&amp;pd_rd_w=E5PCS&amp;pd_rd_wg=13fO7&amp;pf_rd_p=14238797-2284-4030-be73-f85ec6483cda&amp;pf_rd_r=6WN8AJ1Z0XX78FXEGP9Z&amp;qid=1762375517&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=kugelbahn%2Caps%2C116&amp;sr=1-2-cab768cc-b5f2-405d-95e3-d2dfa86c6f23-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9zZWFyY2hfdGhlbWF0aWNfYnRm&amp;th=1</t>
+  </si>
+  <si>
+    <t>Gravi Tax Entension Trax</t>
+  </si>
+  <si>
+    <t>Ravensburger GraviTrax Extension Trax 22414  Erweiterung</t>
+  </si>
+  <si>
+    <t>Jack Power PCB 25x</t>
   </si>
 </sst>
 </file>
@@ -186,7 +225,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +273,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="40"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -250,18 +311,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -429,6 +490,86 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -436,7 +577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -475,31 +616,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -519,6 +648,79 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -877,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5785CA-F4AE-4464-AE2C-5F7A426F62CB}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
@@ -887,27 +1089,37 @@
     <col min="7" max="7" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="25"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="24"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -921,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
@@ -929,13 +1141,15 @@
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -952,8 +1166,10 @@
       <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -977,30 +1193,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="20">
-        <v>1</v>
-      </c>
-      <c r="D6" s="20" t="s">
+      <c r="C6" s="16">
+        <v>1</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="18">
         <v>8.15</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1020,10 +1236,10 @@
         <v>1.89</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1047,7 +1263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1070,66 +1286,83 @@
       <c r="G9" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="J9" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="15">
-        <v>1</v>
-      </c>
-      <c r="D10" s="15" t="s">
+      <c r="C10" s="16">
+        <v>1</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <v>250</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="J10" s="32"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="34"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
         <v>8</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="15">
-        <v>1</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="16">
+        <v>1</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="17"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="34"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F12" s="10">
         <v>16.989999999999998</v>
@@ -1137,8 +1370,13 @@
       <c r="G12" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="37"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1149,7 +1387,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
@@ -1159,44 +1397,57 @@
         <v>5.78</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="J13" s="38">
+        <f>SUM(F4:F51)</f>
+        <v>446.97</v>
+      </c>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="40"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C14" s="7">
-        <v>3</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F14" s="10">
         <v>9.5500000000000007</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="43"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>17</v>
@@ -1207,19 +1458,24 @@
       <c r="G15" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J15" s="41"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="43"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" s="7">
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>17</v>
@@ -1230,19 +1486,24 @@
       <c r="G16" s="8" t="s">
         <v>11</v>
       </c>
+      <c r="J16" s="44"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="46"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>17</v>
@@ -1251,7 +1512,7 @@
         <v>1.94</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1259,13 +1520,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>34</v>
+      <c r="D18" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>17</v>
@@ -1274,7 +1535,7 @@
         <v>1.69</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,13 +1543,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C19" s="7">
-        <v>2</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>17</v>
@@ -1301,34 +1562,154 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20" s="47">
         <v>17</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="7">
-        <v>3</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>12</v>
+      <c r="B20" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="48">
+        <v>1</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="51">
+        <v>35.99</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="47">
+        <v>18</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="48">
+        <v>1</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="51">
+        <v>19.79</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="7">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="10">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>20</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="7">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="10">
+        <f>C23 * 1.19</f>
+        <v>3.57</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="10">
+        <f>C24 * 3.02</f>
+        <v>3.02</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="10">
+        <f>C25 * 53.99</f>
+        <v>53.99</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="J13:N16"/>
     <mergeCell ref="A1:G2"/>
+    <mergeCell ref="J9:N12"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G20">
+  <conditionalFormatting sqref="G4:G25">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -1339,8 +1720,8 @@
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G20" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G25" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A15C8E9-D928-488E-B372-50AD469C1D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958E12CD-F6E9-4DFB-A74D-4148E3C97609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21705" yWindow="-12390" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bills Of Material" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM Transceiver" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="70">
   <si>
     <t>No.</t>
   </si>
@@ -216,6 +217,36 @@
   </si>
   <si>
     <t>Jack Power PCB 25x</t>
+  </si>
+  <si>
+    <t>ESP-32 C3 Super Mini</t>
+  </si>
+  <si>
+    <t>In stock</t>
+  </si>
+  <si>
+    <t>TFT 1,8 Inch RGB Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vollfarb-TFT-LCD-Anzeigemodul 128 x 160 SPI, ST7735S</t>
+  </si>
+  <si>
+    <t>Button</t>
+  </si>
+  <si>
+    <t>Coloured Button For directions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP4056 </t>
+  </si>
+  <si>
+    <t>Charger Module</t>
+  </si>
+  <si>
+    <t>TP4057 IC</t>
+  </si>
+  <si>
+    <t>Charger Module IC 50x</t>
   </si>
 </sst>
 </file>
@@ -577,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -631,6 +662,49 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -649,10 +723,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -665,7 +735,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -679,55 +749,34 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1090,34 +1139,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="21"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="36"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="39"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1141,8 +1184,6 @@
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1166,8 +1207,6 @@
       <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1286,13 +1325,13 @@
       <c r="G9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="31"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="42"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
@@ -1316,11 +1355,11 @@
       <c r="G10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="34"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="45"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
@@ -1342,11 +1381,11 @@
       <c r="G11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="34"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="45"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -1370,11 +1409,11 @@
       <c r="G12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="35"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="37"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="48"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1399,14 +1438,14 @@
       <c r="G13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13" s="25">
         <f>SUM(F4:F51)</f>
         <v>446.97</v>
       </c>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="40"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="27"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1430,11 +1469,11 @@
       <c r="G14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="41"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="43"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="30"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1456,13 +1495,13 @@
         <v>1.35</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="41"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="43"/>
+        <v>37</v>
+      </c>
+      <c r="J15" s="28"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="30"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -1486,11 +1525,11 @@
       <c r="G16" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="44"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="46"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="33"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1558,26 +1597,26 @@
         <v>1.99</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="47">
+      <c r="A20" s="20">
         <v>17</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="48">
-        <v>1</v>
-      </c>
-      <c r="D20" s="49" t="s">
+      <c r="C20" s="21">
+        <v>1</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="24">
         <v>35.99</v>
       </c>
       <c r="G20" s="8" t="s">
@@ -1585,22 +1624,22 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="47">
+      <c r="A21" s="20">
         <v>18</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="48">
-        <v>1</v>
-      </c>
-      <c r="D21" s="49" t="s">
+      <c r="C21" s="21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="24">
         <v>19.79</v>
       </c>
       <c r="G21" s="8" t="s">
@@ -1651,7 +1690,7 @@
         <v>3.57</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1710,13 +1749,13 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G4:G25">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1731,4 +1770,271 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4D4044-5250-4025-9307-388FF700D563}">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="42.42578125" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="36"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="39"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="10">
+        <f>C4 * 4.49</f>
+        <v>4.49</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="10">
+        <f>C5 * 2.3</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="10">
+        <f>C6 * 1</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="10">
+        <f>C7 * 2.13</f>
+        <v>2.13</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="10">
+        <f>C8 * 2.15</f>
+        <v>2.15</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J9" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="42"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J10" s="43"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="45"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J11" s="43"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="45"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="46"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="48"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J13" s="25">
+        <f>SUM(F4:F30)</f>
+        <v>12.07</v>
+      </c>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="27"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="30"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J15" s="28"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="30"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="31"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="J9:N12"/>
+    <mergeCell ref="J13:N16"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <conditionalFormatting sqref="G4:G8">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Not ordered"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Ordered"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"In Stock"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G8" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
+      <formula1>"In stock,Ordered,Not ordered"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958E12CD-F6E9-4DFB-A74D-4148E3C97609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C11571-14D0-41B0-B6D0-C3EFB5CC75D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="-12390" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
   <si>
     <t>No.</t>
   </si>
@@ -247,6 +247,30 @@
   </si>
   <si>
     <t>Charger Module IC 50x</t>
+  </si>
+  <si>
+    <t>BSS84W-7-F</t>
+  </si>
+  <si>
+    <t>P Channel MOSFET 50V 50x</t>
+  </si>
+  <si>
+    <t>USB C Female Port</t>
+  </si>
+  <si>
+    <t>USB Type C Female Port 10x</t>
+  </si>
+  <si>
+    <t>Battery Terminal Connector</t>
+  </si>
+  <si>
+    <t>2 Pins Terminal Connector</t>
+  </si>
+  <si>
+    <t>Slide Switch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK12D07 Kippschalter 3PIN </t>
   </si>
 </sst>
 </file>
@@ -1952,6 +1976,28 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="10">
+        <f>C9 * 3.89</f>
+        <v>3.89</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="J9" s="40" t="s">
         <v>50</v>
       </c>
@@ -1961,6 +2007,28 @@
       <c r="N9" s="42"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="10">
+        <f>C10 * 1.29</f>
+        <v>1.29</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="J10" s="43"/>
       <c r="K10" s="44"/>
       <c r="L10" s="44"/>
@@ -1968,6 +2036,28 @@
       <c r="N10" s="45"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="10">
+        <f>C11 * 1.77</f>
+        <v>1.77</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="J11" s="43"/>
       <c r="K11" s="44"/>
       <c r="L11" s="44"/>
@@ -1975,6 +2065,28 @@
       <c r="N11" s="45"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="10">
+        <f>C12 * 2.12</f>
+        <v>2.12</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -1984,7 +2096,7 @@
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J13" s="25">
         <f>SUM(F4:F30)</f>
-        <v>12.07</v>
+        <v>21.14</v>
       </c>
       <c r="K13" s="26"/>
       <c r="L13" s="26"/>
@@ -2019,7 +2131,7 @@
     <mergeCell ref="J13:N16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G8">
+  <conditionalFormatting sqref="G4:G12">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -2031,7 +2143,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G8" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G12" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C11571-14D0-41B0-B6D0-C3EFB5CC75D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63AFBC0-4D22-4A6F-A92E-B07AB99D9DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21705" yWindow="-12390" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
   <si>
     <t>No.</t>
   </si>
@@ -219,24 +219,12 @@
     <t>Jack Power PCB 25x</t>
   </si>
   <si>
-    <t>ESP-32 C3 Super Mini</t>
-  </si>
-  <si>
-    <t>In stock</t>
-  </si>
-  <si>
     <t>TFT 1,8 Inch RGB Display</t>
   </si>
   <si>
     <t xml:space="preserve"> Vollfarb-TFT-LCD-Anzeigemodul 128 x 160 SPI, ST7735S</t>
   </si>
   <si>
-    <t>Button</t>
-  </si>
-  <si>
-    <t>Coloured Button For directions</t>
-  </si>
-  <si>
     <t xml:space="preserve">TP4056 </t>
   </si>
   <si>
@@ -271,6 +259,24 @@
   </si>
   <si>
     <t xml:space="preserve">SK12D07 Kippschalter 3PIN </t>
+  </si>
+  <si>
+    <t>SMD-Diode SOD-123</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SMD-Diode 0805 SOD-123 S4 1N5819 100x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP-WROOM-32 </t>
+  </si>
+  <si>
+    <t>CP2102 WIFI Bluetooth-Modul Dual Core Wireless-Modul ESP-32 ESP-WROOM-32</t>
+  </si>
+  <si>
+    <t>25PCS Tactile Push Button Switch Momentary 12*12*7,3MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tacitile Push Button </t>
   </si>
 </sst>
 </file>
@@ -1860,23 +1866,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <f>C4 * 4.49</f>
-        <v>4.49</v>
+        <f>C4 * 3.79</f>
+        <v>3.79</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1884,13 +1890,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>17</v>
@@ -1908,20 +1914,20 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="10">
-        <f>C6 * 1</f>
-        <v>1</v>
+        <f>C6 * 1.59</f>
+        <v>1.59</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>11</v>
@@ -1932,13 +1938,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>17</v>
@@ -1956,13 +1962,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>17</v>
@@ -1980,13 +1986,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>17</v>
@@ -1996,7 +2002,7 @@
         <v>3.89</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="J9" s="40" t="s">
         <v>50</v>
@@ -2011,13 +2017,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>17</v>
@@ -2027,7 +2033,7 @@
         <v>1.29</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="J10" s="43"/>
       <c r="K10" s="44"/>
@@ -2040,13 +2046,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>17</v>
@@ -2056,7 +2062,7 @@
         <v>1.77</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="J11" s="43"/>
       <c r="K11" s="44"/>
@@ -2069,13 +2075,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>17</v>
@@ -2085,7 +2091,7 @@
         <v>2.12</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
@@ -2094,9 +2100,31 @@
       <c r="N12" s="48"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="10">
+        <f>C13 * 2.15</f>
+        <v>2.15</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="J13" s="25">
         <f>SUM(F4:F30)</f>
-        <v>21.14</v>
+        <v>23.18</v>
       </c>
       <c r="K13" s="26"/>
       <c r="L13" s="26"/>
@@ -2131,7 +2159,7 @@
     <mergeCell ref="J13:N16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G12">
+  <conditionalFormatting sqref="G4:G13">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -2142,8 +2170,8 @@
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G12" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G13" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63AFBC0-4D22-4A6F-A92E-B07AB99D9DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDA4E2D-E441-413A-81B4-54D370246057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="-12390" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -195,9 +195,6 @@
     <t>TCRT5000</t>
   </si>
   <si>
-    <t>Infrarot Reflektierende Sensor IR 10x</t>
-  </si>
-  <si>
     <t>Solder Station</t>
   </si>
   <si>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tacitile Push Button </t>
+  </si>
+  <si>
+    <t>Infrarot Reflektierende Sensor IR 4x</t>
   </si>
 </sst>
 </file>
@@ -638,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -779,6 +779,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1235,7 +1241,7 @@
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1259,7 +1265,7 @@
         <v>7.38</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1353,7 +1359,7 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="J9" s="40" t="s">
         <v>50</v>
@@ -1470,7 +1476,7 @@
       </c>
       <c r="J13" s="25">
         <f>SUM(F4:F51)</f>
-        <v>446.97</v>
+        <v>448.42000000000007</v>
       </c>
       <c r="K13" s="26"/>
       <c r="L13" s="26"/>
@@ -1488,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>36</v>
@@ -1553,7 +1559,7 @@
         <v>3.69</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="J16" s="31"/>
       <c r="K16" s="32"/>
@@ -1644,7 +1650,7 @@
         <v>34</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" s="24">
         <v>35.99</v>
@@ -1658,16 +1664,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="21">
-        <v>1</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>58</v>
-      </c>
       <c r="E21" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F21" s="24">
         <v>19.79</v>
@@ -1731,20 +1737,20 @@
         <v>51</v>
       </c>
       <c r="C24" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="10">
-        <f>C24 * 3.02</f>
-        <v>3.02</v>
+        <f>C24 * 1.49</f>
+        <v>4.47</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1752,16 +1758,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="7">
-        <v>1</v>
-      </c>
-      <c r="D25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="F25" s="10">
         <f>C25 * 53.99</f>
@@ -1799,6 +1805,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K0000FF internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1808,7 +1817,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="77.5703125" customWidth="1"/>
     <col min="5" max="5" width="31.140625" style="6" customWidth="1"/>
     <col min="6" max="6" width="25.42578125" style="11" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" customWidth="1"/>
@@ -1866,13 +1875,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="C4" s="7">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>17</v>
@@ -1882,7 +1891,7 @@
         <v>3.79</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1890,13 +1899,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>60</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>61</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>17</v>
@@ -1906,7 +1915,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1914,13 +1923,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>17</v>
@@ -1930,26 +1939,26 @@
         <v>1.59</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7" s="15">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="16">
+        <v>1</v>
+      </c>
+      <c r="D7" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="E7" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="18">
         <f>C7 * 2.13</f>
         <v>2.13</v>
       </c>
@@ -1962,13 +1971,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>64</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>65</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>17</v>
@@ -1986,13 +1995,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>17</v>
@@ -2017,13 +2026,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>17</v>
@@ -2046,13 +2055,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>71</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>17</v>
@@ -2075,13 +2084,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>72</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>73</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>17</v>
@@ -2104,13 +2113,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>74</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>75</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>17</v>
@@ -2170,11 +2179,14 @@
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G13" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K0000FF internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDA4E2D-E441-413A-81B4-54D370246057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5D7A36-C04E-409F-8CE0-6A8D6C22E2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21600" yWindow="-9210" windowWidth="21810" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="79">
   <si>
     <t>No.</t>
   </si>
@@ -66,12 +66,6 @@
     <t>USB-C Cable</t>
   </si>
   <si>
-    <t>USB-C Cable 3m</t>
-  </si>
-  <si>
-    <t>https://www.amazon.de/ANMIEL-Typ-C-Kabel-Ladekabel-Datenkabel-geflochten/dp/B09C3HH7KJ/ref=sr_1_6?__mk_de_DE=%C3%85M%C3%85%C5%BD%C3%95%C3%91&amp;crid=1HUJ8X6PSQNU8&amp;dib=eyJ2IjoiMSJ9.ZH0eL8XvX3DTxCgYcgGTokPY-OCGP9OmCfUbJRX_O8dVp8Y1XLwoEsrPFcvnPVLZvmFR-zCeVbO2opkI9v6wstHb3PzAZOQLPOyeihnSe59NsRuwoXQmF8VlHnoIDHRuSmQaxgReVVoqtUnIHtv6TfrKTgO9Kh6iiAGngLh5Ulc8iYjsqR6B1GuoUGYiygCZirhfQUZHJkvbFNL__RF-xSf5BIU2C9X4cmz_-YjN3Lo.3DULeIhGb1u3SODSffwhRyhMYPrRy90LZrRDQ7fSg-g&amp;dib_tag=se&amp;keywords=usb%2Bc%2Bkabel%2Bdata%2B3m&amp;qid=1761953154&amp;sprefix=usb%2Bc%2Bkabel%2Bdata%2B3m%2Caps%2C103&amp;sr=8-6&amp;th=1</t>
-  </si>
-  <si>
     <t>Not ordered</t>
   </si>
   <si>
@@ -135,9 +129,6 @@
     <t>Cer. Capacitors</t>
   </si>
   <si>
-    <t>300 teile/los 50 V 2PF-0,1 UF 30</t>
-  </si>
-  <si>
     <t>Gravi Tax Marble Run</t>
   </si>
   <si>
@@ -277,6 +268,12 @@
   </si>
   <si>
     <t>Infrarot Reflektierende Sensor IR 4x</t>
+  </si>
+  <si>
+    <t>In stock</t>
+  </si>
+  <si>
+    <t>300 teile/los 50 V 2PF-0,1 UF 30 THT</t>
   </si>
 </sst>
 </file>
@@ -638,7 +635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -693,9 +690,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -708,6 +702,12 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -779,12 +779,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1164,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5785CA-F4AE-4464-AE2C-5F7A426F62CB}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
@@ -1175,26 +1169,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="37"/>
       <c r="J1" s="19"/>
       <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="37"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="40"/>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
     </row>
@@ -1212,7 +1206,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
@@ -1226,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -1235,546 +1229,543 @@
         <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" s="10">
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
+        <f>A4 + 1</f>
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="7">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" s="10">
         <f>C5 * 3.69</f>
         <v>7.38</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="1">
+        <f t="shared" ref="A6:A24" si="0">A5 + 1</f>
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="16">
-        <v>1</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="18">
-        <v>8.15</v>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1.89</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="10">
-        <v>1.89</v>
+        <f>C7 * 8.29</f>
+        <v>8.2899999999999991</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" s="10">
-        <f>C8 * 8.29</f>
-        <v>8.2899999999999991</v>
+        <f>C8 * 2.47</f>
+        <v>4.9400000000000004</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="B9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="16">
+        <v>1</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="18">
+        <v>250</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="43"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="10">
-        <f>C9 * 2.47</f>
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="42"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>13</v>
-      </c>
       <c r="C10" s="16">
         <v>1</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="18">
-        <v>250</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F10" s="18"/>
       <c r="G10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="43"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="45"/>
+        <v>9</v>
+      </c>
+      <c r="J10" s="44"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="46"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="16">
-        <v>1</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="18"/>
+      <c r="B11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="10">
+        <v>16.989999999999998</v>
+      </c>
       <c r="G11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="45"/>
+        <v>9</v>
+      </c>
+      <c r="J11" s="44"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="46"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C12" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="F12" s="10">
-        <v>16.989999999999998</v>
+        <f>C12 * 2.89</f>
+        <v>5.78</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="46"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="48"/>
+        <v>77</v>
+      </c>
+      <c r="J12" s="47"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="49"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C13" s="7">
-        <v>2</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F13" s="10">
-        <f>C13 * 2.89</f>
-        <v>5.78</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="25">
-        <f>SUM(F4:F51)</f>
-        <v>448.42000000000007</v>
-      </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="27"/>
+        <v>34</v>
+      </c>
+      <c r="J13" s="26">
+        <f>SUM(F4:F50)</f>
+        <v>440.2700000000001</v>
+      </c>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7">
         <v>1</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>58</v>
+      <c r="D14" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F14" s="10">
-        <v>9.5500000000000007</v>
+        <v>1.35</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="28"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="30"/>
+        <v>34</v>
+      </c>
+      <c r="J14" s="29"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="31"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" s="10">
-        <v>1.35</v>
+        <v>3.69</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="30"/>
+        <v>34</v>
+      </c>
+      <c r="J15" s="29"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="31"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="7">
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" s="10">
-        <v>3.69</v>
+        <v>1.94</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" s="31"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="33"/>
+        <v>77</v>
+      </c>
+      <c r="J16" s="32"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="34"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>29</v>
+      <c r="D17" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" s="10">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" s="10">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="B19" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="20">
+        <v>1</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="23">
+        <v>35.99</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="F19" s="10">
-        <v>1.99</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
-        <v>17</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="21">
-        <v>1</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="24">
-        <v>35.99</v>
+      <c r="B20" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="23">
+        <v>19.79</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="21">
-        <v>1</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="24">
-        <v>19.79</v>
+      <c r="B21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="10">
+        <v>2.4900000000000002</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C22" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" s="10">
-        <v>2.4900000000000002</v>
+        <f>C22 * 1.19</f>
+        <v>3.57</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C23" s="7">
         <v>3</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" s="10">
-        <f>C23 * 1.19</f>
-        <v>3.57</v>
+        <f>C23 * 1.49</f>
+        <v>4.47</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="7">
-        <v>3</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F24" s="10">
-        <f>C24 * 1.49</f>
-        <v>4.47</v>
+        <f>C24 * 53.99</f>
+        <v>53.99</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>22</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="7">
-        <v>1</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="10">
-        <f>C25 * 53.99</f>
-        <v>53.99</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1784,7 +1775,7 @@
     <mergeCell ref="J9:N12"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G25">
+  <conditionalFormatting sqref="G4:G24">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -1796,12 +1787,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G25" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G24" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E12" r:id="rId1" xr:uid="{E8A5AAF1-A457-44FF-B03E-B13CD56D10C7}"/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{E8A5AAF1-A457-44FF-B03E-B13CD56D10C7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1824,26 +1815,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="37"/>
       <c r="J1" s="19"/>
       <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="37"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="40"/>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
     </row>
@@ -1861,7 +1852,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
@@ -1875,23 +1866,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" s="10">
         <f>C4 * 3.79</f>
         <v>3.79</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1899,23 +1890,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" s="10">
         <f>C5 * 2.3</f>
         <v>2.2999999999999998</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1923,23 +1914,23 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" s="10">
         <f>C6 * 1.59</f>
         <v>1.59</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1947,23 +1938,23 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C7" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>17</v>
+      <c r="D7" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>15</v>
       </c>
       <c r="F7" s="18">
         <f>C7 * 2.13</f>
         <v>2.13</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1971,23 +1962,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" s="10">
         <f>C8 * 2.15</f>
         <v>2.15</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1995,171 +1986,171 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" s="10">
         <f>C9 * 3.89</f>
         <v>3.89</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="42"/>
+        <v>34</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="43"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" s="10">
         <f>C10 * 1.29</f>
         <v>1.29</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="43"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="45"/>
+        <v>34</v>
+      </c>
+      <c r="J10" s="44"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="46"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" s="10">
         <f>C11 * 1.77</f>
         <v>1.77</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="45"/>
+        <v>34</v>
+      </c>
+      <c r="J11" s="44"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="46"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" s="10">
         <f>C12 * 2.12</f>
         <v>2.12</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="46"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="48"/>
+        <v>34</v>
+      </c>
+      <c r="J12" s="47"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="49"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" s="10">
         <f>C13 * 2.15</f>
         <v>2.15</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="25">
+        <v>34</v>
+      </c>
+      <c r="J13" s="26">
         <f>SUM(F4:F30)</f>
         <v>23.18</v>
       </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J14" s="28"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="30"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="31"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J15" s="28"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="30"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="31"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J16" s="31"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="33"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5D7A36-C04E-409F-8CE0-6A8D6C22E2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA3408E-DDEE-4368-8046-19043322DD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-9210" windowWidth="21810" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -1235,7 +1235,7 @@
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1507,7 +1507,7 @@
         <v>1.35</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="J14" s="29"/>
       <c r="K14" s="30"/>
@@ -1618,7 +1618,7 @@
         <v>1.99</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1715,7 +1715,7 @@
         <v>3.57</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1978,7 +1978,7 @@
         <v>2.15</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA3408E-DDEE-4368-8046-19043322DD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D0246-E77C-408E-A086-41AD5C7A6D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21600" yWindow="1770" windowWidth="21810" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
   <si>
     <t>No.</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>300 teile/los 50 V 2PF-0,1 UF 30 THT</t>
+  </si>
+  <si>
+    <t>Master Screen 5x</t>
   </si>
 </sst>
 </file>
@@ -785,7 +788,28 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1776,13 +1800,13 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G4:G24">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="J13" s="26">
         <f>SUM(F4:F30)</f>
-        <v>23.18</v>
+        <v>33.14</v>
       </c>
       <c r="K13" s="27"/>
       <c r="L13" s="27"/>
@@ -2132,6 +2156,28 @@
       <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f t="shared" ref="A14" si="0">A13 + 1</f>
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="10">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="J14" s="29"/>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
@@ -2160,6 +2206,17 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G4:G13">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"Not ordered"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Ordered"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"In Stock"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -2171,7 +2228,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G13" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G14" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D0246-E77C-408E-A086-41AD5C7A6D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CFD9FF-A04B-479E-8AF8-1F032290B25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="1770" windowWidth="21810" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -788,28 +788,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -1259,7 +1238,7 @@
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1333,7 +1312,7 @@
         <v>8.2899999999999991</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1800,13 +1779,13 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G4:G24">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2205,18 +2184,7 @@
     <mergeCell ref="J13:N16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G13">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"Not ordered"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"Ordered"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
-      <formula>"In Stock"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
+  <conditionalFormatting sqref="G4:G14">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D0246-E77C-408E-A086-41AD5C7A6D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFF8AE7-99B5-4EED-8851-048D6BC75531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21600" yWindow="1770" windowWidth="21810" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
@@ -153,9 +153,6 @@
     <t>16V 1000uF 10x10.2</t>
   </si>
   <si>
-    <t>Adapter 5V 10A</t>
-  </si>
-  <si>
     <t>Netzteil Adapter AC 220V DC  5V 10A</t>
   </si>
   <si>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t>Master Screen 5x</t>
+  </si>
+  <si>
+    <t>PSU 5V 10A</t>
   </si>
 </sst>
 </file>
@@ -788,28 +788,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -1259,7 +1238,7 @@
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1308,7 +1287,7 @@
         <v>1.89</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1385,7 +1364,7 @@
         <v>9</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="42"/>
       <c r="L9" s="42"/>
@@ -1425,16 +1404,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>40</v>
       </c>
       <c r="F11" s="10">
         <v>16.989999999999998</v>
@@ -1460,7 +1439,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>15</v>
@@ -1470,7 +1449,7 @@
         <v>5.78</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J12" s="47"/>
       <c r="K12" s="48"/>
@@ -1490,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>33</v>
@@ -1531,7 +1510,7 @@
         <v>1.35</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J14" s="29"/>
       <c r="K14" s="30"/>
@@ -1551,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>15</v>
@@ -1589,7 +1568,7 @@
         <v>1.94</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J16" s="32"/>
       <c r="K16" s="33"/>
@@ -1609,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>15</v>
@@ -1618,7 +1597,7 @@
         <v>1.69</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1642,7 +1621,7 @@
         <v>1.99</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1660,7 +1639,7 @@
         <v>31</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F19" s="23">
         <v>35.99</v>
@@ -1675,16 +1654,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="20">
-        <v>1</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>54</v>
-      </c>
       <c r="E20" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F20" s="23">
         <v>19.79</v>
@@ -1699,13 +1678,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>15</v>
@@ -1714,7 +1693,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1723,13 +1702,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="7">
         <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>15</v>
@@ -1739,7 +1718,7 @@
         <v>3.57</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1748,13 +1727,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="7">
         <v>3</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>15</v>
@@ -1773,16 +1752,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="7">
-        <v>1</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="F24" s="10">
         <f>C24 * 53.99</f>
@@ -1800,13 +1779,13 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G4:G24">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Ordered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"In Stock"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1890,13 +1869,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="C4" s="7">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>15</v>
@@ -1914,13 +1893,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>57</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>15</v>
@@ -1938,13 +1917,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>15</v>
@@ -1962,13 +1941,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="16">
+        <v>1</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>58</v>
-      </c>
-      <c r="C7" s="16">
-        <v>1</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>59</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>15</v>
@@ -1986,13 +1965,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>60</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>61</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>15</v>
@@ -2002,7 +1981,7 @@
         <v>2.15</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -2010,13 +1989,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>62</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>63</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>15</v>
@@ -2029,7 +2008,7 @@
         <v>34</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="42"/>
       <c r="L9" s="42"/>
@@ -2041,13 +2020,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>64</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>65</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>15</v>
@@ -2070,13 +2049,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>15</v>
@@ -2099,13 +2078,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>15</v>
@@ -2128,13 +2107,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>71</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>15</v>
@@ -2167,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>33</v>
@@ -2205,18 +2184,7 @@
     <mergeCell ref="J13:N16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G13">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"Not ordered"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"Ordered"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
-      <formula>"In Stock"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
+  <conditionalFormatting sqref="G4:G14">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CFD9FF-A04B-479E-8AF8-1F032290B25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB6DDA2-47D9-48C6-950E-8D2883942B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21600" yWindow="1770" windowWidth="21810" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -78,9 +78,6 @@
     <t>3D Printer up to 250€</t>
   </si>
   <si>
-    <t>(black Friday)</t>
-  </si>
-  <si>
     <t>Servo SG90 9g</t>
   </si>
   <si>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t>Master Screen 5x</t>
+  </si>
+  <si>
+    <t>Kleineinzeigen</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -1232,13 +1232,13 @@
         <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="10">
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1247,23 +1247,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="10">
         <f>C5 * 3.69</f>
         <v>7.38</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1278,16 +1278,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="10">
         <v>1.89</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1296,23 +1296,23 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" s="10">
         <f>C7 * 8.29</f>
         <v>8.2899999999999991</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1321,23 +1321,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="7">
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="10">
         <f>C8 * 2.47</f>
         <v>4.9400000000000004</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1355,16 +1355,16 @@
         <v>12</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F9" s="18">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="42"/>
       <c r="L9" s="42"/>
@@ -1377,13 +1377,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="16">
+        <v>1</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>21</v>
-      </c>
-      <c r="C10" s="16">
-        <v>1</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>22</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>10</v>
@@ -1404,16 +1404,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>40</v>
       </c>
       <c r="F11" s="10">
         <v>16.989999999999998</v>
@@ -1433,23 +1433,23 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="7">
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" s="10">
         <f>C12 * 2.89</f>
         <v>5.78</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J12" s="47"/>
       <c r="K12" s="48"/>
@@ -1463,26 +1463,26 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>32</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>33</v>
       </c>
       <c r="F13" s="10">
         <v>9.5500000000000007</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" s="26">
         <f>SUM(F4:F50)</f>
-        <v>440.2700000000001</v>
+        <v>290.27000000000004</v>
       </c>
       <c r="K13" s="27"/>
       <c r="L13" s="27"/>
@@ -1495,22 +1495,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="E14" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="10">
         <v>1.35</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J14" s="29"/>
       <c r="K14" s="30"/>
@@ -1524,22 +1524,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="10">
         <v>3.69</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J15" s="29"/>
       <c r="K15" s="30"/>
@@ -1553,22 +1553,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="7">
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" s="10">
         <v>1.94</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J16" s="32"/>
       <c r="K16" s="33"/>
@@ -1582,22 +1582,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="10">
         <v>1.69</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1606,22 +1606,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="7">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>37</v>
-      </c>
       <c r="E18" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" s="10">
         <v>1.99</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1630,16 +1630,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="20">
+        <v>1</v>
+      </c>
+      <c r="D19" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="20">
-        <v>1</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>31</v>
-      </c>
       <c r="E19" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F19" s="23">
         <v>35.99</v>
@@ -1654,16 +1654,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="20">
-        <v>1</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>54</v>
-      </c>
       <c r="E20" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F20" s="23">
         <v>19.79</v>
@@ -1678,22 +1678,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="7">
-        <v>1</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="E21" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" s="10">
         <v>2.4900000000000002</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1702,23 +1702,23 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="7">
         <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" s="10">
         <f>C22 * 1.19</f>
         <v>3.57</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1727,23 +1727,23 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="7">
         <v>3</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" s="10">
         <f>C23 * 1.49</f>
         <v>4.47</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1752,16 +1752,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="7">
-        <v>1</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="F24" s="10">
         <f>C24 * 53.99</f>
@@ -1855,7 +1855,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>6</v>
@@ -1869,23 +1869,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="7">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="E4" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="10">
         <f>C4 * 3.79</f>
         <v>3.79</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1893,23 +1893,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="7">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>57</v>
-      </c>
       <c r="E5" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="10">
         <f>C5 * 2.3</f>
         <v>2.2999999999999998</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1917,23 +1917,23 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="10">
         <f>C6 * 1.59</f>
         <v>1.59</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1941,16 +1941,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="16">
+        <v>1</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="16">
-        <v>1</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>59</v>
-      </c>
       <c r="E7" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" s="18">
         <f>C7 * 2.13</f>
@@ -1965,23 +1965,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>61</v>
-      </c>
       <c r="E8" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="10">
         <f>C8 * 2.15</f>
         <v>2.15</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1989,26 +1989,26 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>63</v>
-      </c>
       <c r="E9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" s="10">
         <f>C9 * 3.89</f>
         <v>3.89</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="42"/>
       <c r="L9" s="42"/>
@@ -2020,23 +2020,23 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>65</v>
-      </c>
       <c r="E10" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" s="10">
         <f>C10 * 1.29</f>
         <v>1.29</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J10" s="44"/>
       <c r="K10" s="45"/>
@@ -2049,23 +2049,23 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="E11" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" s="10">
         <f>C11 * 1.77</f>
         <v>1.77</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="44"/>
       <c r="K11" s="45"/>
@@ -2078,23 +2078,23 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>69</v>
-      </c>
       <c r="E12" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" s="10">
         <f>C12 * 2.12</f>
         <v>2.12</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" s="47"/>
       <c r="K12" s="48"/>
@@ -2107,23 +2107,23 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>71</v>
-      </c>
       <c r="E13" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" s="10">
         <f>C13 * 2.15</f>
         <v>2.15</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" s="26">
         <f>SUM(F4:F30)</f>
@@ -2140,22 +2140,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>33</v>
       </c>
       <c r="F14" s="10">
         <v>9.9600000000000009</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J14" s="29"/>
       <c r="K14" s="30"/>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB6DDA2-47D9-48C6-950E-8D2883942B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4AC9F4-C146-4CC4-A4C8-0AEA246A06D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="1770" windowWidth="21810" windowHeight="15930" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -357,7 +357,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,6 +380,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -638,7 +644,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -782,6 +788,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1238,7 +1253,7 @@
         <v>4.49</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1263,7 +1278,7 @@
         <v>7.38</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1337,7 +1352,7 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1478,7 +1493,7 @@
         <v>9.5500000000000007</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="J13" s="26">
         <f>SUM(F4:F50)</f>
@@ -1539,7 +1554,7 @@
         <v>3.69</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="J15" s="29"/>
       <c r="K15" s="30"/>
@@ -1743,7 +1758,7 @@
         <v>4.47</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1885,7 +1900,7 @@
         <v>3.79</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1909,7 +1924,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1933,7 +1948,7 @@
         <v>1.59</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -2005,7 +2020,7 @@
         <v>3.89</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="J9" s="41" t="s">
         <v>46</v>
@@ -2036,7 +2051,7 @@
         <v>1.29</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="J10" s="44"/>
       <c r="K10" s="45"/>
@@ -2045,27 +2060,27 @@
       <c r="N10" s="46"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="A11" s="51">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="20">
+        <v>1</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="E11" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="23">
         <f>C11 * 1.77</f>
         <v>1.77</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>33</v>
+      <c r="G11" s="50" t="s">
+        <v>76</v>
       </c>
       <c r="J11" s="44"/>
       <c r="K11" s="45"/>
@@ -2094,7 +2109,7 @@
         <v>2.12</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="J12" s="47"/>
       <c r="K12" s="48"/>
@@ -2123,7 +2138,7 @@
         <v>2.15</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="J13" s="26">
         <f>SUM(F4:F30)</f>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4AC9F4-C146-4CC4-A4C8-0AEA246A06D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161BBF87-2FF6-48B0-8E51-12C76FCAA547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="6450" windowWidth="21810" windowHeight="18945" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -717,6 +717,15 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -788,15 +797,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1187,26 +1187,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
       <c r="J1" s="19"/>
       <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="38"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="40"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
     </row>
@@ -1378,13 +1378,13 @@
       <c r="G9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="43"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1407,11 +1407,11 @@
       <c r="G10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="46"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="49"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1434,13 +1434,13 @@
         <v>16.989999999999998</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="44"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="46"/>
+        <v>33</v>
+      </c>
+      <c r="J11" s="47"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="49"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -1466,11 +1466,11 @@
       <c r="G12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="47"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="52"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1495,14 +1495,14 @@
       <c r="G13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="29">
         <f>SUM(F4:F50)</f>
-        <v>290.27000000000004</v>
-      </c>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="28"/>
+        <v>271.07000000000005</v>
+      </c>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1527,11 +1527,11 @@
       <c r="G14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="29"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="31"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="34"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1556,11 +1556,11 @@
       <c r="G15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="29"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="31"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="34"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -1585,11 +1585,11 @@
       <c r="G16" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="34"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="37"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1657,10 +1657,10 @@
         <v>51</v>
       </c>
       <c r="F19" s="23">
-        <v>35.99</v>
+        <v>28.89</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1681,10 +1681,10 @@
         <v>50</v>
       </c>
       <c r="F20" s="23">
-        <v>19.79</v>
+        <v>15.99</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1779,11 +1779,11 @@
         <v>50</v>
       </c>
       <c r="F24" s="10">
-        <f>C24 * 53.99</f>
-        <v>53.99</v>
+        <f>C24 * 45.69</f>
+        <v>45.69</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1833,26 +1833,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
       <c r="J1" s="19"/>
       <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="38"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="40"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
     </row>
@@ -2022,13 +2022,13 @@
       <c r="G9" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="43"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2053,14 +2053,14 @@
       <c r="G10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="46"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="49"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="51">
+      <c r="A11" s="27">
         <v>8</v>
       </c>
       <c r="B11" s="20" t="s">
@@ -2072,21 +2072,21 @@
       <c r="D11" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="28" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="23">
         <f>C11 * 1.77</f>
         <v>1.77</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="G11" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="44"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="46"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="49"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -2111,11 +2111,11 @@
       <c r="G12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="47"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="49"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="52"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2140,14 +2140,14 @@
       <c r="G13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="29">
         <f>SUM(F4:F30)</f>
         <v>33.14</v>
       </c>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="28"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2172,25 +2172,25 @@
       <c r="G14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="29"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="31"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="34"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J15" s="29"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="31"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="34"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J16" s="32"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="34"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161BBF87-2FF6-48B0-8E51-12C76FCAA547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03131F2-D98C-4EF3-8761-CFFB7CC9064F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03131F2-D98C-4EF3-8761-CFFB7CC9064F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B12207-6F2F-4E5A-A064-97DD1B75A839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-21600" yWindow="-3405" windowWidth="21810" windowHeight="15930" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="89">
   <si>
     <t>No.</t>
   </si>
@@ -277,6 +277,33 @@
   </si>
   <si>
     <t>Kleineinzeigen</t>
+  </si>
+  <si>
+    <t>ESP-32 Bluetooth- und WIFI-Dual-Core-CPU</t>
+  </si>
+  <si>
+    <t>EC11</t>
+  </si>
+  <si>
+    <t>EC11 Button + Dreher 5x</t>
+  </si>
+  <si>
+    <t>Black Cap EC11</t>
+  </si>
+  <si>
+    <t>Black Cap for EC11 5x</t>
+  </si>
+  <si>
+    <t>TFT 3.5 Inch</t>
+  </si>
+  <si>
+    <t>3,5-Zoll-TFT-LCD-Modul mit Touchpanel ILI9488-Treiber 320 x 480</t>
+  </si>
+  <si>
+    <t>Master Prototype V2.00</t>
+  </si>
+  <si>
+    <t>Production for Master Screen V2.00</t>
   </si>
 </sst>
 </file>
@@ -1822,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4D4044-5250-4025-9307-388FF700D563}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
@@ -2142,7 +2169,7 @@
       </c>
       <c r="J13" s="29">
         <f>SUM(F4:F30)</f>
-        <v>33.14</v>
+        <v>44.76</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -2151,7 +2178,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <f t="shared" ref="A14" si="0">A13 + 1</f>
+        <f t="shared" ref="A14:A19" si="0">A13 + 1</f>
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -2179,6 +2206,28 @@
       <c r="N14" s="34"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1.89</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="J15" s="32"/>
       <c r="K15" s="33"/>
       <c r="L15" s="33"/>
@@ -2186,11 +2235,105 @@
       <c r="N15" s="34"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f>A15 + 1</f>
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1.94</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="J16" s="35"/>
       <c r="K16" s="36"/>
       <c r="L16" s="36"/>
       <c r="M16" s="36"/>
       <c r="N16" s="37"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1.23</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="10">
+        <v>6.56</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="7">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2199,7 +2342,7 @@
     <mergeCell ref="J13:N16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G14">
+  <conditionalFormatting sqref="G4:G19">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -2211,7 +2354,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G14" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G19" xr:uid="{5C30DADA-6449-478F-B571-319D09B3C008}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ruben\Documents\Git\Marble-Station-ESP32\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B12207-6F2F-4E5A-A064-97DD1B75A839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F21828C-F427-4893-8B19-01A9F94872AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-3405" windowWidth="21810" windowHeight="15930" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -399,12 +399,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -412,6 +406,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -671,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -713,117 +713,102 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1214,28 +1199,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1396,22 +1381,22 @@
       <c r="D9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <v>100</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="44" t="s">
+      <c r="J9" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="46"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="40"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1427,18 +1412,18 @@
       <c r="D10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="18"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="47"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="49"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="43"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1463,11 +1448,11 @@
       <c r="G11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="47"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="49"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="43"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -1493,11 +1478,11 @@
       <c r="G12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="50"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="52"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="46"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1522,14 +1507,14 @@
       <c r="G13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="23">
         <f>SUM(F4:F50)</f>
         <v>271.07000000000005</v>
       </c>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="31"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1554,11 +1539,11 @@
       <c r="G14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="34"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1583,11 +1568,11 @@
       <c r="G15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="34"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -1612,11 +1597,11 @@
       <c r="G16" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="37"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="31"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1671,19 +1656,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="20">
-        <v>1</v>
-      </c>
-      <c r="D19" s="21" t="s">
+      <c r="C19" s="16">
+        <v>1</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="19">
         <v>28.89</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -1695,19 +1680,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="20">
-        <v>1</v>
-      </c>
-      <c r="D20" s="21" t="s">
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="19">
         <v>15.99</v>
       </c>
       <c r="G20" s="8" t="s">
@@ -1860,28 +1845,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1979,7 +1964,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="21">
         <v>4</v>
       </c>
       <c r="B7" s="16" t="s">
@@ -1988,18 +1973,18 @@
       <c r="C7" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="18">
+      <c r="E7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="19">
         <f>C7 * 2.13</f>
         <v>2.13</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>9</v>
+      <c r="G7" s="47" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2049,13 +2034,13 @@
       <c r="G9" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="44" t="s">
+      <c r="J9" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="46"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="40"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2080,40 +2065,40 @@
       <c r="G10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="47"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="49"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="43"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="27">
+      <c r="A11" s="21">
         <v>8</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="20">
-        <v>1</v>
-      </c>
-      <c r="D11" s="21" t="s">
+      <c r="C11" s="16">
+        <v>1</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="23">
+      <c r="E11" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="19">
         <f>C11 * 1.77</f>
         <v>1.77</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="47"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="49"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="43"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -2138,11 +2123,11 @@
       <c r="G12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="50"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="52"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="46"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2167,14 +2152,14 @@
       <c r="G13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="23">
         <f>SUM(F4:F30)</f>
         <v>44.76</v>
       </c>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="31"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2199,11 +2184,11 @@
       <c r="G14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="34"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2228,11 +2213,11 @@
       <c r="G15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="34"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -2257,11 +2242,11 @@
       <c r="G16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="37"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="31"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">

--- a/parts/Marble-Station-Part-List.xlsx
+++ b/parts/Marble-Station-Part-List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\r.sahetapy\Documents\Git\Marble-Station-ESP32\parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F21828C-F427-4893-8B19-01A9F94872AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B72EFA-D024-4AF1-9CC6-86ECD100B99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C4091438-3C34-46B4-BEF6-AD84959AFF8F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM Receiver" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>No.</t>
   </si>
@@ -304,6 +304,15 @@
   </si>
   <si>
     <t>Production for Master Screen V2.00</t>
+  </si>
+  <si>
+    <t>Jack Power PCB 10x</t>
+  </si>
+  <si>
+    <t>Teminal Block</t>
+  </si>
+  <si>
+    <t>Terminal Block 3.5mm 2P 50x</t>
   </si>
 </sst>
 </file>
@@ -735,6 +744,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,9 +818,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1188,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5785CA-F4AE-4464-AE2C-5F7A426F62CB}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.42578125" customWidth="1"/>
@@ -1199,26 +1208,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
       <c r="J1" s="15"/>
       <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="38"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
     </row>
@@ -1295,7 +1304,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A24" si="0">A5 + 1</f>
+        <f t="shared" ref="A6:A26" si="0">A5 + 1</f>
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -1339,7 +1348,7 @@
         <v>8.2899999999999991</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1390,13 +1399,13 @@
       <c r="G9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="41"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1419,11 +1428,11 @@
       <c r="G10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="41"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="43"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="44"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1448,11 +1457,11 @@
       <c r="G11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="41"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="43"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="44"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -1478,11 +1487,11 @@
       <c r="G12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="44"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="46"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="47"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1495,26 +1504,26 @@
       <c r="C13" s="7">
         <v>1</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>54</v>
+      <c r="D13" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>32</v>
       </c>
       <c r="F13" s="10">
-        <v>9.5500000000000007</v>
+        <v>7.43</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="23">
-        <f>SUM(F4:F50)</f>
-        <v>271.07000000000005</v>
-      </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="25"/>
+        <v>33</v>
+      </c>
+      <c r="J13" s="24">
+        <f>SUM(F4:F51)</f>
+        <v>284.08</v>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1522,28 +1531,28 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C14" s="7">
         <v>1</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>25</v>
+      <c r="D14" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F14" s="10">
-        <v>1.35</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="28"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="29"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1551,28 +1560,28 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="10">
-        <v>3.69</v>
+        <v>1.35</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="26"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="28"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="29"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -1586,22 +1595,22 @@
         <v>1</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="10">
-        <v>1.94</v>
+        <v>3.69</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="29"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="31"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="32"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1609,19 +1618,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>77</v>
+      <c r="D17" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="10">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>76</v>
@@ -1633,19 +1642,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="10">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>76</v>
@@ -1656,23 +1665,23 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="16">
-        <v>1</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="19">
-        <v>28.89</v>
+      <c r="B19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="10">
+        <v>1.99</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1681,22 +1690,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C20" s="16">
         <v>1</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" s="19">
-        <v>15.99</v>
+        <v>28.89</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1704,20 +1713,20 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="10">
-        <v>2.4900000000000002</v>
+      <c r="B21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="16">
+        <v>1</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="19">
+        <v>15.99</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>76</v>
@@ -1729,20 +1738,19 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="10">
-        <f>C22 * 1.19</f>
-        <v>3.57</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>76</v>
@@ -1754,20 +1762,20 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C23" s="7">
         <v>3</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="10">
-        <f>C23 * 1.49</f>
-        <v>4.47</v>
+        <f>C23 * 1.19</f>
+        <v>3.57</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>76</v>
@@ -1779,22 +1787,72 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="7">
+        <v>3</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="10">
+        <f>C24 * 1.49</f>
+        <v>4.47</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="7">
-        <v>1</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E25" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="10">
-        <f>C24 * 45.69</f>
+      <c r="F25" s="10">
+        <f>C25 * 45.69</f>
         <v>45.69</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G25" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="10">
+        <f>C26 * 2.79</f>
+        <v>5.58</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1805,7 +1863,7 @@
     <mergeCell ref="J9:N12"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="G4:G24">
+  <conditionalFormatting sqref="G4:G26">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Not ordered"</formula>
     </cfRule>
@@ -1817,7 +1875,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G24" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G26" xr:uid="{69404353-99F0-41F3-8F9D-7E5C48143DF8}">
       <formula1>"In stock,Ordered,Not ordered"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1845,26 +1903,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
       <c r="J1" s="15"/>
       <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="38"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
     </row>
@@ -1983,7 +2041,7 @@
         <f>C7 * 2.13</f>
         <v>2.13</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="23" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2034,13 +2092,13 @@
       <c r="G9" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="41"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -2065,11 +2123,11 @@
       <c r="G10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="41"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="43"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="44"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
@@ -2094,11 +2152,11 @@
       <c r="G11" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="41"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="43"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="44"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -2123,11 +2181,11 @@
       <c r="G12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="44"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="46"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="47"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2152,14 +2210,14 @@
       <c r="G13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="24">
         <f>SUM(F4:F30)</f>
         <v>44.76</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2184,11 +2242,11 @@
       <c r="G14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="28"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="29"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2213,11 +2271,11 @@
       <c r="G15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J15" s="26"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="28"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="29"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -2242,11 +2300,11 @@
       <c r="G16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J16" s="29"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="31"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="32"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
